--- a/healthcare_surveys/003_digital_detox_behavior_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/003_digital_detox_behavior_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the Digital Detox Behavior Survey.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,158 +542,186 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>screen_time_habits</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>screen_time_habits</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How many hours do you spend on screens each day?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the exact number of hours spent on screens.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1_answer</t>
+          <t>digital_device_ownership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>screen_time_habits_answer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Do you own a smartphone?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Do you own a smartphone?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>digital_device_ownership_answer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>digital_device_usage</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How many other digital devices do you own?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please specify the number of devices you own.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2_answer</t>
+          <t>digital_device_usage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question_2_answer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How often do you use your digital devices?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select your usage frequency.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>digital_device_impact_on_routine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Do you feel anxious without a digital device?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Do you feel anxious without a digital device?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3_answer</t>
+          <t>digital_device_restrictions_effectiveness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question_3_answer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Do you feel more focused without digital devices?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Do you feel more focused without digital devices?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>digital_device_social_usage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you use your digital devices during social gatherings?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Do you use devices during social gatherings?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_4_answer</t>
+          <t>digital_device_entertainment_usage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question_4_answer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you use your digital devices for entertainment?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Do you use devices for entertainment?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>digital_device_owning_multiple_devices</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you own multiple digital devices?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Do you own multiple devices?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5_answer</t>
+          <t>digital_device_usage_work_school</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question_5_answer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Do you use digital devices for work or school?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Do you use devices for work or school?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>digital_device_usage_social_media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Do you use social media often?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Do you use social media often?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_6_answer</t>
+          <t>digital_device_usage_news_information</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question_6_answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you follow news sources online?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Do you follow news sources online?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>digital_device_usage_learning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Do you use devices for learning?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Do you use devices for learning?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_7_answer</t>
+          <t>digital_device_usage_creative_activities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>question_7_answer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Do you use devices for creative activities?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Do you use devices for creative activities?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>digital_device_usage_for_relaxation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Do you use devices to relax?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Do you use devices to relax?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_8_answer</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>question_8_answer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Thank you for participating in the Digital Detox Behavior Survey.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,23 +974,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>demographics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Are you willing to participate in the survey?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -934,179 +1006,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question_9_answer</t>
+          <t>demographics_answer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>question_9_answer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>What is your age group?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please select your age group.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_10_answer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question_10_answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>digital_device_ownership</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_11_answer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>question_11_answer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>conclusion</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>conclusion</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>demographics</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>demographics</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>demographics_answer</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>demographics_answer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1036,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,408 +1064,544 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>digital_device_ownership_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>digital_device_ownership_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>digital_device_usage_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>digital_device_usage_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>digital_device_usage_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>digital_device_impact_on_routine_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>digital_device_impact_on_routine_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>digital_device_restrictions_effectiveness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>digital_device_restrictions_effectiveness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>digital_device_social_usage_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>digital_device_social_usage_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>digital_device_social_usage_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>digital_device_entertainment_usage_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>digital_device_entertainment_usage_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>digital_device_owning_multiple_devices_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>digital_device_owning_multiple_devices_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>digital_device_usage_work_school_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>digital_device_usage_work_school_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>digital_device_usage_work_school_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>digital_device_usage_social_media_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>digital_device_usage_social_media_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>digital_device_usage_news_information_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>demographics_choices</t>
+          <t>digital_device_usage_news_information_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>digital_device_usage_news_information_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>digital_device_usage_learning_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>digital_device_usage_learning_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>digital_device_usage_creative_activities_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>digital_device_usage_creative_activities_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>digital_device_usage_for_relaxation_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>digital_device_usage_for_relaxation_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>demographics_choices</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>demographics_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
